--- a/data/trans_camb/KIDM_A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_A_R-Clase-trans_camb.xlsx
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,54</t>
+          <t>0,0; 12,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -692,32 +692,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,25; 0,0</t>
+          <t>-14,87; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,43; 6,02</t>
+          <t>-9,0; 7,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-15,37; 0,0</t>
+          <t>-13,99; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 4,4</t>
+          <t>-3,99; 3,93</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 4,07</t>
+          <t>-4,17; 4,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 0,0</t>
+          <t>-7,3; 0,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 4,02</t>
+          <t>-10,55; 4,08</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,79; 2,3</t>
+          <t>-12,03; 2,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 10,49</t>
+          <t>-8,71; 10,25</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,9; 0,0</t>
+          <t>-11,31; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,93; 0,0</t>
+          <t>-13,79; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,53; 0,0</t>
+          <t>-14,22; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 0,94</t>
+          <t>-8,19; 0,94</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 0,59</t>
+          <t>-8,72; 0,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,21; 4,02</t>
+          <t>-6,26; 3,81</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,96; 1,94</t>
+          <t>-13,39; 1,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-12,15; 4,44</t>
+          <t>-11,64; 4,52</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,31; 0,0</t>
+          <t>-15,01; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 4,53</t>
+          <t>-7,15; 4,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,88; 3,9</t>
+          <t>-8,17; 3,89</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 13,09</t>
+          <t>-6,67; 9,84</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,69; 2,01</t>
+          <t>-7,23; 1,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,4; 2,29</t>
+          <t>-6,93; 2,36</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 4,44</t>
+          <t>-6,76; 5,01</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 252,18</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 212,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; inf</t>
         </is>
       </c>
     </row>
@@ -1325,27 +1325,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 9,02</t>
+          <t>-0,83; 7,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 4,1</t>
+          <t>-2,59; 4,62</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 3,73</t>
+          <t>-3,23; 4,59</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,68; 10,54</t>
+          <t>2,25; 10,41</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,18; 10,08</t>
+          <t>1,17; 10,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,56; 7,73</t>
+          <t>1,84; 7,71</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,17; 5,07</t>
+          <t>0,22; 5,04</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 1,49</t>
+          <t>-1,83; 1,43</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>41,49; —</t>
+          <t>16,63; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-43,14; —</t>
+          <t>-47,31; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,29; 3,06</t>
+          <t>-6,68; 3,06</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,95; 2,77</t>
+          <t>-7,41; 2,87</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-7,72; 2,0</t>
+          <t>-8,39; 1,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,48; 7,67</t>
+          <t>-2,33; 7,46</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,8; 0,0</t>
+          <t>-8,24; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 0,0</t>
+          <t>-7,84; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 3,86</t>
+          <t>-3,06; 3,81</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 0,82</t>
+          <t>-4,79; 0,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,84; -0,08</t>
+          <t>-5,61; -0,21</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-72,92; 487,02</t>
+          <t>-80,65; 447,54</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1757,22 +1757,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 20,4</t>
+          <t>-1,68; 19,08</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 0,0</t>
+          <t>-8,37; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-7,47; 0,0</t>
+          <t>-8,26; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,57; 12,9</t>
+          <t>1,57; 13,91</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,43; 19,52</t>
+          <t>2,28; 18,71</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,54; 12,75</t>
+          <t>0,59; 12,28</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,0</t>
+          <t>-4,59; 0,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 9,28</t>
+          <t>-0,58; 9,34</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 3,87</t>
+          <t>-0,92; 3,71</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,56; 1,08</t>
+          <t>-2,38; 1,41</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 1,18</t>
+          <t>-2,82; 1,14</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 4,24</t>
+          <t>-0,51; 3,84</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,69</t>
+          <t>-2,13; 1,72</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,41; 1,24</t>
+          <t>-2,52; 1,15</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 3,14</t>
+          <t>-0,13; 3,16</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,97</t>
+          <t>-1,77; 0,96</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 0,74</t>
+          <t>-2,14; 0,74</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-33,85; 300,88</t>
+          <t>-36,9; 343,69</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-76,58; 109,26</t>
+          <t>-76,15; 149,13</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-89,32; 121,62</t>
+          <t>-87,52; 145,24</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-15,41; 412,27</t>
+          <t>-26,38; 350,51</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-75,31; 145,19</t>
+          <t>-72,54; 202,45</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-83,03; 190,73</t>
+          <t>-87,27; 135,33</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 233,09</t>
+          <t>-8,59; 228,07</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-59,12; 75,25</t>
+          <t>-62,34; 72,56</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-74,94; 67,03</t>
+          <t>-75,8; 69,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/KIDM_A_R-Clase-trans_camb.xlsx
+++ b/data/trans_camb/KIDM_A_R-Clase-trans_camb.xlsx
@@ -523,7 +523,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores con salud general autopercibida regular o mala (autopercepción menor)</t>
+          <t>Menores cuya salud general autopercibida es regular o mala</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,7 +677,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,72</t>
+          <t>0,0; 13,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -692,32 +692,32 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 0,0</t>
+          <t>-15,16; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-9,0; 7,16</t>
+          <t>-10,01; 5,83</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,99; 0,0</t>
+          <t>-14,47; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 3,93</t>
+          <t>-4,2; 4,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 4,07</t>
+          <t>-4,11; 3,12</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 0,0</t>
+          <t>-7,26; 0,0</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,55; 4,08</t>
+          <t>-9,86; 4,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-12,03; 2,28</t>
+          <t>-11,88; 2,28</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-8,71; 10,25</t>
+          <t>-7,72; 10,68</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,31; 0,0</t>
+          <t>-13,63; 0,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 0,0</t>
+          <t>-13,88; 0,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,22; 0,0</t>
+          <t>-15,4; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 0,94</t>
+          <t>-8,77; 0,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,72; 0,59</t>
+          <t>-9,04; 0,59</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 3,81</t>
+          <t>-6,9; 3,58</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 1,72</t>
+          <t>-12,8; 1,76</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 4,52</t>
+          <t>-12,37; 4,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 0,0</t>
+          <t>-17,61; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,15; 4,94</t>
+          <t>-8,13; 5,23</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 3,89</t>
+          <t>-8,12; 3,88</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 9,84</t>
+          <t>-6,67; 9,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,23; 1,96</t>
+          <t>-7,05; 2,03</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,93; 2,36</t>
+          <t>-7,54; 2,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-6,76; 5,01</t>
+          <t>-7,01; 4,19</t>
         </is>
       </c>
     </row>
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 237,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 212,83</t>
+          <t>-100,0; 202,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; inf</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1325,27 +1325,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 7,92</t>
+          <t>-0,7; 8,99</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-2,59; 4,62</t>
+          <t>-2,58; 4,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,23; 4,59</t>
+          <t>-3,28; 3,7</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,25; 10,41</t>
+          <t>2,64; 10,4</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>1,17; 10,0</t>
+          <t>1,23; 9,98</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1355,17 +1355,17 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,84; 7,71</t>
+          <t>1,78; 8,01</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 5,04</t>
+          <t>-0,02; 5,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 1,43</t>
+          <t>-1,66; 1,64</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,63; —</t>
+          <t>52,23; —</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-47,31; —</t>
+          <t>-55,41; —</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 3,06</t>
+          <t>-7,18; 3,04</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 2,87</t>
+          <t>-7,2; 2,88</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,39; 1,91</t>
+          <t>-7,7; 2,16</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 7,46</t>
+          <t>-2,13; 8,22</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 0,0</t>
+          <t>-6,82; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 0,0</t>
+          <t>-7,17; 0,0</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 3,81</t>
+          <t>-2,3; 4,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 0,7</t>
+          <t>-4,65; 0,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-5,61; -0,21</t>
+          <t>-5,15; -0,07</t>
         </is>
       </c>
     </row>
@@ -1677,12 +1677,12 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-80,65; 447,54</t>
+          <t>-70,0; 552,88</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1757,22 +1757,22 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 19,08</t>
+          <t>-1,48; 21,34</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 0,0</t>
+          <t>-8,46; 0,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 0,0</t>
+          <t>-8,73; 0,0</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1,57; 13,91</t>
+          <t>1,6; 13,77</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,28; 18,71</t>
+          <t>2,38; 18,38</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,59; 12,28</t>
+          <t>0,8; 12,5</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,0</t>
+          <t>-5,45; 0,0</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 9,34</t>
+          <t>-0,32; 9,47</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 3,71</t>
+          <t>-1,03; 3,76</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,41</t>
+          <t>-2,41; 1,16</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 1,14</t>
+          <t>-2,73; 1,24</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 3,84</t>
+          <t>-0,3; 4,13</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 1,72</t>
+          <t>-1,94; 1,87</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 1,15</t>
+          <t>-2,67; 1,22</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,16</t>
+          <t>-0,23; 3,09</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 0,96</t>
+          <t>-1,6; 1,03</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 0,74</t>
+          <t>-2,12; 0,65</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-36,9; 343,69</t>
+          <t>-32,54; 371,34</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-76,15; 149,13</t>
+          <t>-77,43; 119,32</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-87,52; 145,24</t>
+          <t>-87,96; 151,38</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 350,51</t>
+          <t>-18,21; 361,7</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-72,54; 202,45</t>
+          <t>-69,55; 221,03</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-87,27; 135,33</t>
+          <t>-86,65; 164,2</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-8,59; 228,07</t>
+          <t>-11,09; 229,45</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-62,34; 72,56</t>
+          <t>-59,54; 79,47</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-75,8; 69,0</t>
+          <t>-77,06; 57,62</t>
         </is>
       </c>
     </row>
